--- a/output/pdf_financials_xlsx/HOT.UN.xlsx
+++ b/output/pdf_financials_xlsx/HOT.UN.xlsx
@@ -16452,7 +16452,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -56592,7 +56596,7 @@
         </is>
       </c>
       <c r="E629" s="5" t="n">
-        <v>0.454864</v>
+        <v>-0.454864</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/HOT.UN.xlsx
+++ b/output/pdf_financials_xlsx/HOT.UN.xlsx
@@ -17928,7 +17928,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">

--- a/output/pdf_financials_xlsx/HOT.UN.xlsx
+++ b/output/pdf_financials_xlsx/HOT.UN.xlsx
@@ -964,7 +964,7 @@
         <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>-3.5165</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1736,7 +1736,7 @@
         <v>-0.454864</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.924</v>
+        <v>2.5925</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1.011</v>
@@ -1830,7 +1830,7 @@
         <v>-0.454864</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5.444</v>
+        <v>8.9605</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>12.72</v>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11.3293931574128</v>
+        <v>18.64750686756014</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>13.65642077236078</v>
@@ -5824,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.142353</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -36301,7 +36301,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -54820,7 +54824,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E607" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HOT.UN.xlsx
+++ b/output/pdf_financials_xlsx/HOT.UN.xlsx
@@ -1150,7 +1150,7 @@
         <v>0.454864</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-2.44668</v>
+        <v>0.752</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>1.213</v>
@@ -1928,7 +1928,7 @@
         <v>-100</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-228.6616822429907</v>
+        <v>-70.28037383177571</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>132.568306010929</v>
@@ -5548,19 +5548,19 @@
         <v>0.08411399999999999</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>2.695</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-3.716</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-5.344</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>11.241</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>4.925</v>
@@ -19423,7 +19423,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -22426,7 +22430,11 @@
           <t>Deferred income tax (expense) recovery</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -24018,7 +24026,11 @@
           <t>Deferred income tax recovery 7</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -29064,7 +29076,11 @@
           <t>Deferred income tax recovery 8(b)</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -29143,7 +29159,11 @@
           <t>Change in non-cash operating working capital 19(a)</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -30484,7 +30504,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -30559,7 +30583,11 @@
           <t>Change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -31598,7 +31626,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -31835,7 +31867,11 @@
           <t>Change in non-cash operating working capital 21</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -33184,7 +33220,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -33502,7 +33542,11 @@
           <t>Changes in non-cash operating working capital 20</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -35019,7 +35063,11 @@
           <t>Changes in non-cash operating working capital 20</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -36467,7 +36515,11 @@
           <t>Changes in non-cash operating working capital (Note 16)</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E374" s="5" t="n">
         <v>0.08411399999999999</v>
       </c>
@@ -40412,7 +40464,11 @@
           <t>Current income tax recovery 7</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -44455,7 +44511,11 @@
           <t>Deferred income tax recovery 7</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -47299,7 +47359,11 @@
           <t>Deferred income tax (recovery)/expense</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
@@ -51057,7 +51121,11 @@
           <t>Deferred income tax recovery 8</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E560" t="inlineStr">
         <is>
           <t>-</t>
@@ -51608,7 +51676,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E567" t="inlineStr">
         <is>
           <t>-</t>
@@ -52807,7 +52879,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
           <t>-</t>
